--- a/ctl-site/src/assets/CATL.xlsx
+++ b/ctl-site/src/assets/CATL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\ctl-angular\ctl-angular\src\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9be54d10f24db4ff/CTL site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260EA5DC-4F81-4A07-BB33-3D2366529A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3F3CFC0-12B6-4484-A00E-2F5B1C1086C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1200" windowWidth="17280" windowHeight="10632" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet_1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,270 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="25">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="15"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="16"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="18"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="20"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="25">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+    <bk>
+      <rc t="1" v="8"/>
+    </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
+    </bk>
+    <bk>
+      <rc t="1" v="11"/>
+    </bk>
+    <bk>
+      <rc t="1" v="12"/>
+    </bk>
+    <bk>
+      <rc t="1" v="13"/>
+    </bk>
+    <bk>
+      <rc t="1" v="14"/>
+    </bk>
+    <bk>
+      <rc t="1" v="15"/>
+    </bk>
+    <bk>
+      <rc t="1" v="16"/>
+    </bk>
+    <bk>
+      <rc t="1" v="17"/>
+    </bk>
+    <bk>
+      <rc t="1" v="18"/>
+    </bk>
+    <bk>
+      <rc t="1" v="19"/>
+    </bk>
+    <bk>
+      <rc t="1" v="20"/>
+    </bk>
+    <bk>
+      <rc t="1" v="21"/>
+    </bk>
+    <bk>
+      <rc t="1" v="22"/>
+    </bk>
+    <bk>
+      <rc t="1" v="23"/>
+    </bk>
+    <bk>
+      <rc t="1" v="24"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>DESCRIÇÃO COMPLETA</t>
   </si>
@@ -49,13 +311,54 @@
   <si>
     <t>DESCRIÇÃO PEQUENA 
 (Topo da página)</t>
+  </si>
+  <si>
+    <t>Cada CRIANÇA, uma OPORTUNIDADE!</t>
+  </si>
+  <si>
+    <t>[Periodos letivos] Tarde: 17h30 às 19h30 — para crianças que saem da escola e precisam de apoio até os pais poderem recolher na escola;</t>
+  </si>
+  <si>
+    <t>Interrupções letivas (férias escolares, pausas, etc.):  das 07h30 às 19h30;</t>
+  </si>
+  <si>
+    <t>Este horário longo permite apoiar famílias que trabalham para além do horário escolar, cobrindo tanto manhãs cedo como fim de tarde, e oferecendo também ocupação no período das férias;</t>
+  </si>
+  <si>
+    <t>A funcionar durante todos os meses do ano civil;</t>
+  </si>
+  <si>
+    <t>O CATL é uma resposta social para os “tempos livres” de crianças/jovens em idade escolar (1.º ciclo) — i.e., quando não estão nas aulas, antes da escola de manhã ou depois da escola à tarde, e durante interrupções letivas. 
+Tem uma Equipa multidisciplinar, pelo que inclui animadores socioculturais, educadores sociais e professores de educação física, música, teatro entre outros especialistas, — garantindo um acompanhamento educativo e social adequado. 
+O serviço tem um “amplo projeto sociocultural” com atividades diversificadas, adaptadas à faixa etária, propiciando o crescimento pessoal, a socialização, o apoio educativo e desenvolvimento de interesses diversos. Proporciona um espaço educativo e de convívio fora do horário escolar, com atividades que incentivam o desenvolvimento global das crianças — intelectual, social, cultural e recreativo.</t>
+  </si>
+  <si>
+    <t>Serviços Prestados:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funcionamento do CATL: </t>
+  </si>
+  <si>
+    <t>Locais onde desesenvolvemos a resposta Social: CATL de Almas de Freire e de Assafarge [localizados nas EB1] |  TOTAL: 110 Vagas;</t>
+  </si>
+  <si>
+    <t>Natação [Adaptação ao meio aquático e desenvolvimento técnico]: Piscinas Municipais Luís Lopres da Conceição,</t>
+  </si>
+  <si>
+    <t>Apoio na realização dos trabalhos de casa;</t>
+  </si>
+  <si>
+    <t>Aulas de música e de instrumento [ex. guitarra, bateria, canto, baixo , piano, entre outros];</t>
+  </si>
+  <si>
+    <t>Apoio pedagógico especializado [ex. língua portuguesa, matemática, estudo do meio, entre outras áreas];</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,6 +373,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ADLaM Display"/>
     </font>
   </fonts>
   <fills count="5">
@@ -138,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -170,6 +478,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -185,6 +496,190 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="25">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>10</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>11</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>12</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>13</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>14</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>15</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>16</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>17</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>18</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>19</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>20</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>21</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>22</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>23</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>24</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
+  <rel r:id="rId12"/>
+  <rel r:id="rId13"/>
+  <rel r:id="rId14"/>
+  <rel r:id="rId15"/>
+  <rel r:id="rId16"/>
+  <rel r:id="rId17"/>
+  <rel r:id="rId18"/>
+  <rel r:id="rId19"/>
+  <rel r:id="rId20"/>
+  <rel r:id="rId21"/>
+  <rel r:id="rId22"/>
+  <rel r:id="rId23"/>
+  <rel r:id="rId24"/>
+  <rel r:id="rId25"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -451,23 +946,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="52.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="41.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.21875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25.5546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="25.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="64.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -493,11 +990,13 @@
       <c r="Y1" s="9"/>
       <c r="Z1" s="9"/>
     </row>
-    <row r="2" spans="1:26" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="207.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -523,11 +1022,13 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -553,17 +1054,31 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -583,11 +1098,13 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -613,14 +1130,22 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -643,37 +1168,87 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C7" s="3" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D7" s="3" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E7" s="3" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" s="3" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G7" s="3" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H7" s="3" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I7" s="3" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J7" s="3" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K7" s="3" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L7" s="3" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M7" s="3" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N7" s="3" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O7" s="3" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P7" s="3" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q7" s="3" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R7" s="3" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="S7" s="3" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T7" s="3" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="U7" s="3" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="V7" s="3" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W7" s="3" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="X7" s="3" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y7" s="3" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z7" s="3" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -701,7 +1276,7 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -729,7 +1304,7 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -757,7 +1332,7 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -785,7 +1360,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -813,7 +1388,7 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -841,7 +1416,7 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -869,7 +1444,7 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -897,7 +1472,7 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -925,7 +1500,7 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -955,6 +1530,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
